--- a/data/trans_dic/P21D_1_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P21D_1_R-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria médica, no la pudo recibir por motivos económicos</t>
+          <t>Población que, necesitando atención sanitaria médica, no la pudo recibir por motivos económicos (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,34</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,41</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,01</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,6</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,13</t>
+          <t>0,0; 1,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,44</t>
+          <t>0,0; 0,5</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,59</t>
+          <t>0,0; 0,64</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,4</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,35</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,3</t>
+          <t>0,0; 0,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria médica, no la pudo recibir por motivos económicos</t>
+          <t>Población que, necesitando atención sanitaria médica, no la pudo recibir por motivos económicos (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1776</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1328</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1527</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1787</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1270</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1492</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4193</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 1165</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2973</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1765</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3835</t>
+          <t>0; 3507</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3485</t>
+          <t>0; 3983</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1719</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3537</t>
+          <t>0; 3551</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3738</t>
+          <t>0; 4079</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4140</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1259</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1566</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 2189</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 4673</t>
+          <t>0; 5149</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 4667</t>
+          <t>0; 4639</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P21D_1_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P21D_1_R-Clase-trans_dic.xlsx
@@ -704,12 +704,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,03</t>
+          <t>0,0; 1,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,5</t>
+          <t>0,0; 0,39</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -777,19 +777,19 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,85</t>
+          <t>0,0; 0,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,64</t>
+          <t>0,0; 0,67</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,33</t>
+          <t>0,0; 0,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,15</t>
+          <t>0,0; 0,16</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>702</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>702</t>
         </is>
       </c>
     </row>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3507</t>
+          <t>0; 4393</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3983</t>
+          <t>0; 3525</t>
         </is>
       </c>
     </row>
@@ -1306,12 +1306,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>749</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>749</t>
         </is>
       </c>
     </row>
@@ -1329,19 +1329,19 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3551</t>
+          <t>0; 3742</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 4079</t>
+          <t>0; 4410</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1451</t>
         </is>
       </c>
     </row>
@@ -1475,12 +1475,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 5149</t>
+          <t>0; 5147</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 4639</t>
+          <t>0; 5079</t>
         </is>
       </c>
     </row>
